--- a/AI Audit Log_NguyenDinhAnhTuan.xlsx
+++ b/AI Audit Log_NguyenDinhAnhTuan.xlsx
@@ -1,48 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FPT_IT\Semester\SU26\SE20C02_LAB211_SU26\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3DB4BAFD-22E4-4A56-8BB6-7291655F4E02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
-    <sheet name="Assignment 1" sheetId="2" r:id="rId2"/>
-    <sheet name="Assignment 2" sheetId="3" r:id="rId3"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Template" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Assignment 1" state="visible" r:id="rId5"/>
+    <sheet sheetId="4" name="Assignment 3" state="visible" r:id="rId6"/>
+    <sheet sheetId="3" name="Assignment 2" state="visible" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+  <si>
+    <t>STT</t>
+  </si>
+  <si>
+    <t>Giai đoạn/Thành phần DTC</t>
+  </si>
+  <si>
+    <t>Nội dung Prompt (Câu lệnh)</t>
+  </si>
+  <si>
+    <t>Phản hồi của AI &amp; Quyết định của người học (Reflection)</t>
+  </si>
   <si>
     <t>Ví dụ: Abstraction</t>
   </si>
@@ -50,72 +34,144 @@
     <t>“Tôi cần quản lý thông tin sinh viên cho app quản lý điểm. Hãy liệt kê các thuộc tính cần thiết."</t>
   </si>
   <si>
+    <t xml:space="preserve">Phản hồi: AI liệt kê 20 thuộc tính._x000d_
+Quyết định: Tôi chỉ chọn 10 thuộc tính liên quan đến chức năng đang được yêu cầu từ ứng dụng (CCCD, địa chỉ...) và lược bỏ 10 thuộc tính học thuật vì phù hợp với yêu cầu của ứng dụng</t>
+  </si>
+  <si>
     <t>Ví dụ: Process/Algorithm</t>
   </si>
   <si>
+    <t>"Viết hàm C sắp xếp mảng sinh viên theo điểm số bằng Selection Sort."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI cung cấp code mẫu._x000d_
+Kiểm chứng: Tôi nhận thấy code AI chưa xử lý trường hợp mảng rỗng (Oversimplification). Tôi đã yêu cầu AI tối ưu lại và tự tay bổ sung điều kiện kiểm tra lỗi.</t>
+  </si>
+  <si>
     <t>Ví dụ: Pattern Recognition</t>
   </si>
   <si>
     <t>“So sánh các giải thuật CPU scheduling: FCFS, SJF, Round Robin, Priority. Giải thuật nào tốt nhất?”</t>
   </si>
   <si>
+    <t xml:space="preserve">Phản hồi: AI response Round Robin là “tốt nhất” vì cân bằng giữa throughput và fairness._x000d_
+Kiểm chứng: AI đưa kết luận sai – không có giải thuật “tốt nhất” tuyệt đối (Hallucination). Mỗi giải thuật phù hợp với tình huống/context khác nhau.</t>
+  </si>
+  <si>
     <t>Ví dụ: Pattern Recognition + Literature Review</t>
   </si>
   <si>
     <t>“Tóm tắt 5 bài báo gần đây nhất về anomaly detection trong IoT sensor data.”</t>
   </si>
   <si>
-    <t>Giai đoạn/Thành phần DTC</t>
-  </si>
-  <si>
-    <t>Nội dung Prompt (Câu lệnh)</t>
-  </si>
-  <si>
-    <t>Phản hồi của AI &amp; Quyết định của người học (Reflection)</t>
-  </si>
-  <si>
-    <t>STT</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI liệt kê 20 thuộc tính.
-Quyết định: Tôi chỉ chọn 10 thuộc tính liên quan đến chức năng đang được yêu cầu từ ứng dụng (CCCD, địa chỉ...) và lược bỏ 10 thuộc tính học thuật vì phù hợp với yêu cầu của ứng dụng</t>
-  </si>
-  <si>
-    <t>"Viết hàm C sắp xếp mảng sinh viên theo điểm số bằng Selection Sort."</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI cung cấp code mẫu.
-Kiểm chứng: Tôi nhận thấy code AI chưa xử lý trường hợp mảng rỗng (Oversimplification). Tôi đã yêu cầu AI tối ưu lại và tự tay bổ sung điều kiện kiểm tra lỗi.</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI response Round Robin là “tốt nhất” vì cân bằng giữa throughput và fairness.
-Kiểm chứng: AI đưa kết luận sai – không có giải thuật “tốt nhất” tuyệt đối (Hallucination). Mỗi giải thuật phù hợp với tình huống/context khác nhau.</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI tóm tắt 5 papers với tên tác giả, năm xuất bản và tóm tắt nội dung.
+    <t xml:space="preserve">Phản hồi: AI tóm tắt 5 papers với tên tác giả, năm xuất bản và tóm tắt nội dung._x000d_
 Kiểm chứng: Tìm trên Google Scholar: 2/5 papers AI nêu là không tồn tại (fabrication). Tôi đã thay bằng 2 papers mà tôi đã tìm kiếm trên research gates và đã kiểm chứng trên google scholar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">State Diagram – Order Lifecycle
+(Decomposition + Process/Algorithm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là một chuyên gia Phân tích Thiết kế Hệ thống (Systems Analyst). Hãy giúp tôi thiết kế một Sơ đồ trạng thái (State Diagram) cho thực thể "Đơn hàng" (Order) trong hệ thống quản lý nhà hàng Vincom (kịch bản ăn tại quán - dine-in) dựa trên các yêu cầu nghiêm ngặt sau:
+### 1. Danh sách các Trạng thái (States) bắt buộc phải có:
+- Trạng thái bắt đầu (Initial State) và Trạng thái kết thúc (Final State) hiển thị bằng ký hiệu [*].
+- Created, Confirmed, Paid, Preparing, ReadyToServe, Served, Completed.
+- Trạng thái thất bại/hủy: PaymentFailed và Cancelled.
+### 2. Danh sách các Sự kiện kích hoạt dịch chuyển (Transitions &amp; Events):
+- [*] -&gt; Created
+- Created -&gt; Confirmed bằng "confirmOrder"
+- Confirmed -&gt; Paid bằng "paySuccess"
+- Confirmed -&gt; PaymentFailed bằng "payFail"
+- PaymentFailed -&gt; Cancelled
+- Created -&gt; Cancelled bằng "cancelOrder"
+- Paid -&gt; Preparing bằng "startCooking"
+- Preparing -&gt; ReadyToServe bằng "finishCooking"
+- ReadyToServe -&gt; Served bằng "serveOrder"
+- Served -&gt; Completed bằng "closeOrder"
+- Cancelled và Completed -&gt; [*].
+### 3. Yêu cầu đầu ra:
+1. Mã nguồn PlantUML trong @startuml/@enduml.
+2. Bảng giải thích chi tiết Transition Table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI cung cấp đầy đủ mã PlantUML cho State Diagram với tất cả 9 trạng thái (Created, Confirmed, Paid, Preparing, ReadyToServe, Served, Completed, PaymentFailed, Cancelled), 12 bước chuyển dịch có ghi rõ triggering event, kèm skinparam tạo màu sắc phân biệt trạng thái thành công (xanh) và thất bại (cam). AI cũng cung cấp bảng Transition Table chi tiết 12 dòng.
+Quyết định: Tôi kiểm tra sơ đồ trên PlantText, xác nhận logic chuyển dịch đúng yêu cầu đề bài, đủ các nhánh rẽ (cancelOrder từ Created, payFail từ Confirmed). Chấp nhận kết quả.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phân tích &amp; Đọc hiểu đề bài
+(Abstraction + Pattern Recognition)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là người thầy cá nhân của tôi. Nhiệm vụ của bạn là làm tôi thông minh hơn sau mỗi nhiệm vụ chúng ta thực hiện cùng nhau.
+Phân tích cách đọc hiểu yêu cầu đề bài, sử dụng ngôn ngữ bình dân để giúp t dễ hiểu, giải thích ko phải kiểu sách giáo khoa khô khan. Tôi muốn sau khi đọc xong, tôi cảm thấy mình thực sự hiểu chuyện gì đã xảy ra và tại sao — chứ không chỉ là nhìn thấy kết quả cuối cùng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI chia bài giảng thành 3 phần: (1) Bí kíp "Mổ xẻ" đề bài – hướng dẫn tìm nhân vật chính, trạng thái, sự kiện; (2) Giải thích từng giai đoạn theo kịch bản thực tế ăn nhà hàng; (3) Rút ra 3 quy tắc vàng: "Không có đường về từ cõi chết", "Mọi con đường dẫn đến Final State", "Một mũi tên một chiếc vé".
+Quyết định: Cách giải thích bằng ví dụ đời thường giúp tôi hiểu rõ bản chất State Diagram. Tôi nắm được tư duy phân tích đề trước khi vẽ sơ đồ. Chấp nhận và áp dụng phương pháp này cho các bài tiếp theo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Activity Diagram – Return Car
+(Decomposition + Process/Algorithm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tương tự như lúc t gửi yêu cầu cho state diagram, giải quyết bài khác sử dụng activity diagram.
+[Đề bài Activity Diagram – Return Car: Mô tả workflow khi khách trả xe thuê, staff kiểm tra tình trạng xe, system xác định phí phụ thu. Yêu cầu: ít nhất 2 swimlane (Staff, System), Decision Node cho phí phụ thu, thể hiện completion of booking và update system status, Level 2 – Design.]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI cung cấp mã PlantUML Activity Diagram với 2 swimlane (Staff và System), có Decision Node rẽ nhánh "Có lỗi/Không lỗi", bao gồm các action: Receive car → Inspect → Submit report → Receive data → Decision → Calculate charges/Generate invoice (nhánh Có) → Request payment → Record payment → Update Booking "Completed" → Update Car "Available" → Send email → End. Kèm bảng Activity Flow Table 10 bước.
+Quyết định: Kiểm tra trên PlantText, sơ đồ render đúng logic, swimlane phân vai rõ ràng, nhánh rẽ hội tụ đúng. Chấp nhận kết quả.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tinh chỉnh đầu ra
+(Refinement / Iteration)</t>
+  </si>
+  <si>
+    <t>sử dụng tiếng anh cho activity diagram chứ ko phải tiếng việt, làm lại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI tạo lại 2 phiên bản PlantUML hoàn toàn bằng tiếng Anh: (1) Sơ đồ chính có swimlane Level 2 Design, (2) Sơ đồ luồng logic rút gọn.
+Quyết định: Yêu cầu chuyển ngữ hợp lý vì bài nộp cần thống nhất ngôn ngữ tiếng Anh theo đề. Chấp nhận bản tiếng Anh để sử dụng chính thức.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm chứng công cụ
+(Pattern Recognition + Abstraction)</t>
+  </si>
+  <si>
+    <t>nếu vẽ trong visual paradigm 17.3 thì nên sử dụng cái gì để chứa các hoạt động trên Activity hay là action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI giải thích sự khác biệt: Activity là cả quy trình (bản thân sơ đồ), Action là từng bước đơn lẻ bên trong (hình chữ nhật bo góc). Với bài này dùng Action vì mỗi bước đều là hành động nguyên tử, không cần phân rã thêm.
+Quyết định: Hiểu rõ sự khác biệt Activity vs Action trong UML 2.x. Áp dụng: dùng Action node trong Visual Paradigm 17.3 cho tất cả các bước trong sơ đồ Return Car.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bây giờ thì phân tích lại cách đọc hiểu đề giống như lúc nãy t yêu cầu
+[Đề: Activity Diagram – Return Car, Level 2 Design, swimlane Staff + System, Decision Node, completion of booking, update system status]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phản hồi: AI phân tích đề thành 5 câu hỏi cốt lõi: (1) Quy trình kể chuyện gì? (2) Có bao nhiêu vai diễn, ai làm gì? (3) Chỗ nào rẽ nhánh? (4) Đề yêu cầu gì ở phần kết? (5) Level 2 Design nghĩa là gì? Kèm theo bản đồ tư duy trước khi vẽ và checklist tự chấm 10 điểm.
+Quyết định: Phương pháp "5 câu hỏi cốt lõi" giúp tôi có framework rõ ràng để phân tích mọi đề Activity Diagram. Checklist 10 mục rất hữu ích để tự kiểm tra trước khi nộp. Ghi nhận và áp dụng.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="163"/>
-      <scheme val="minor"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -136,16 +192,16 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -153,24 +209,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -201,44 +248,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -266,31 +313,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -318,23 +348,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -346,136 +359,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -497,93 +554,87 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
-  <dimension ref="A1:E5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="20.9296875" customWidth="1"/>
-    <col min="2" max="2" width="26.86328125" customWidth="1"/>
-    <col min="3" max="3" width="24.265625" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="2" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="57" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="85.5" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -593,27 +644,133 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A16565-6ACB-4DDB-B0C1-55C7722368A3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="35" customWidth="1"/>
+    <col min="3" max="3" width="45" customWidth="1"/>
+    <col min="4" max="4" width="65" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" ht="300" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" ht="135" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" ht="135" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" ht="75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="105" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr customHeight="1"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
